--- a/LDC.xlsx
+++ b/LDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{0AE175BF-41C4-41B0-BB88-AEEA0AC58EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CC2988F-A632-4305-A02B-C4E9FBAC94D7}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{0AE175BF-41C4-41B0-BB88-AEEA0AC58EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D55F7B5-0BEA-4FFC-8D23-DA1D8DACBC94}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{381F0F33-FFEF-45E1-8129-DD167F3DDD36}"/>
   </bookViews>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T17">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="S27">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T27">
         <v>0</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="S28">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T28">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="S29">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T29">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T30">
         <v>0</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T32">
         <v>0</v>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="S33">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T33">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="S34">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="S35">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="S36">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T36">
         <v>0</v>
@@ -3814,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="S37">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T37">
         <v>0</v>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="S38">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T38">
         <v>0</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="S39">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T39">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T40">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="S41">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T41">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="S42">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T42">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="S43">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T43">
         <v>0</v>
@@ -4395,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T44">
         <v>0</v>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T45">
         <v>0</v>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="S46">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T46">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="S47">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T47">
         <v>0</v>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="S48">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T48">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="S49">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T49">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="S50">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T50">
         <v>0</v>
@@ -4976,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="S51">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T51">
         <v>0</v>
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="S52">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T52">
         <v>0</v>
@@ -5097,7 +5097,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -5142,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="S53">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T53">
         <v>0</v>
@@ -5225,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="S54">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T54">
         <v>0</v>
@@ -5308,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="S55">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T55">
         <v>0</v>
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="S56">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T56">
         <v>0</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="S57">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T57">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="S58">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T58">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="S59">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T59">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="S60">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T60">
         <v>0</v>
@@ -5761,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="S61">
-        <v>2.6756756756756758E-2</v>
+        <v>0</v>
       </c>
       <c r="T61">
         <v>0</v>
@@ -5889,7 +5889,7 @@
         <v>1</v>
       </c>
       <c r="S62">
-        <v>2.6756756756756758E-2</v>
+        <v>1</v>
       </c>
       <c r="T62">
         <v>0.2</v>

--- a/LDC.xlsx
+++ b/LDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{0AE175BF-41C4-41B0-BB88-AEEA0AC58EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D55F7B5-0BEA-4FFC-8D23-DA1D8DACBC94}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{0AE175BF-41C4-41B0-BB88-AEEA0AC58EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC14C1C1-31D6-42C0-B38D-E603F1565F0F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{381F0F33-FFEF-45E1-8129-DD167F3DDD36}"/>
   </bookViews>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="B7">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1715,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R16">
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="B18">
         <v>7.0000000000000007E-2</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>0.19</v>
+        <v>0.03</v>
       </c>
       <c r="B19">
         <v>0.03</v>
@@ -2293,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2444,11 +2444,11 @@
         <v>0</v>
       </c>
       <c r="E21">
+        <v>0.03</v>
+      </c>
+      <c r="F21">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F21">
-        <v>0.03</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2492,13 +2492,13 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="X21">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -2658,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V23">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -5835,79 +5835,79 @@
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>0.66</v>
+        <v>0.97</v>
       </c>
       <c r="B62">
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="F62">
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0.79</v>
+      </c>
+      <c r="R62">
         <v>0.97</v>
       </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0.3</v>
-      </c>
-      <c r="J62">
-        <v>0.2</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0.2</v>
-      </c>
-      <c r="Q62">
-        <v>0.7</v>
-      </c>
-      <c r="R62">
+      <c r="S62">
+        <v>0.999</v>
+      </c>
+      <c r="T62">
         <v>1</v>
       </c>
-      <c r="S62">
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
         <v>1</v>
       </c>
-      <c r="T62">
-        <v>0.2</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>0.5</v>
-      </c>
       <c r="W62">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="X62">
         <v>1</v>
       </c>
       <c r="Y62">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Z62">
         <v>1</v>
